--- a/data/Lead_information_Formulario_Uruguay_Chrome.xlsx
+++ b/data/Lead_information_Formulario_Uruguay_Chrome.xlsx
@@ -1,34 +1,191 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="49">
+  <si>
+    <t>URL</t>
+  </si>
+  <si>
+    <t>Formulario</t>
+  </si>
+  <si>
+    <t>Modelo</t>
+  </si>
+  <si>
+    <t>Nombre</t>
+  </si>
+  <si>
+    <t>Apellido</t>
+  </si>
+  <si>
+    <t>Documento</t>
+  </si>
+  <si>
+    <t>Celular</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Región</t>
+  </si>
+  <si>
+    <t>Ciudad</t>
+  </si>
+  <si>
+    <t>Concesionario</t>
+  </si>
+  <si>
+    <t>Fecha estimada</t>
+  </si>
+  <si>
+    <t>Dispositivo</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.uy/suv/groove-deportivo</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.uy/suv/tracker-suv</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.uy/pickups/s10-high-country-pickup</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.uy/pickups/nueva-montana</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.uy/pickups/silverado-camioneta-pickup</t>
+  </si>
+  <si>
+    <t>https://secure-developments.com/commonwealth/uruguay/gm_front/form/movs-visid-quote?model=groove</t>
+  </si>
+  <si>
+    <t>https://secure-developments.com/commonwealth/uruguay/gm_front/form/movs-visid-quote?model=tracker</t>
+  </si>
+  <si>
+    <t>https://secure-developments.com/commonwealth/uruguay/gm_front/form/movs-visid-quote?model=s10</t>
+  </si>
+  <si>
+    <t>https://secure-developments.com/commonwealth/uruguay/gm_front/form/movs-visid-quote?model=montana</t>
+  </si>
+  <si>
+    <t>https://secure-developments.com/commonwealth/uruguay/gm_front/form/movs-visid-quote?model=silverado</t>
+  </si>
+  <si>
+    <t>Carlos</t>
+  </si>
+  <si>
+    <t>Sebastián</t>
+  </si>
+  <si>
+    <t>Gonzalo Paula</t>
+  </si>
+  <si>
+    <t>Patricia</t>
+  </si>
+  <si>
+    <t>Florencia</t>
+  </si>
+  <si>
+    <t>Figueroa</t>
+  </si>
+  <si>
+    <t>Acosta Jimenez</t>
+  </si>
+  <si>
+    <t>Suarez</t>
+  </si>
+  <si>
+    <t>Torres</t>
+  </si>
+  <si>
+    <t>Serrano</t>
+  </si>
+  <si>
+    <t>91522681</t>
+  </si>
+  <si>
+    <t>40878848</t>
+  </si>
+  <si>
+    <t>84147096</t>
+  </si>
+  <si>
+    <t>91226139</t>
+  </si>
+  <si>
+    <t>68562592</t>
+  </si>
+  <si>
+    <t>098785053</t>
+  </si>
+  <si>
+    <t>097045218</t>
+  </si>
+  <si>
+    <t>097378472</t>
+  </si>
+  <si>
+    <t>093768336</t>
+  </si>
+  <si>
+    <t>095610253</t>
+  </si>
+  <si>
+    <t>carlosfigueroa.uy30_chrome@mrm.com</t>
+  </si>
+  <si>
+    <t>sebastianacostajimenez.uy45_chrome@mrm.com</t>
+  </si>
+  <si>
+    <t>gonzalopaulasuarez_uy55_chrome@mrm.com</t>
+  </si>
+  <si>
+    <t>patriciatorres_uy87_chrome@mrm.com</t>
+  </si>
+  <si>
+    <t>florenciaserrano.uy06_chrome@mrm.com</t>
+  </si>
+  <si>
+    <t>chrome</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <scheme val="minor"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -43,84 +200,23 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -408,82 +504,194 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>URL</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Formulario</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Modelo</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Nombre</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Apellido</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Documento</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Celular</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Región</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Ciudad</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Concesionario</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Fecha estimada</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Dispositivo</t>
-        </is>
+    <row r="1" spans="1:13">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H3" t="s">
+        <v>44</v>
+      </c>
+      <c r="M3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H4" t="s">
+        <v>45</v>
+      </c>
+      <c r="M4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H5" t="s">
+        <v>46</v>
+      </c>
+      <c r="M5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H6" t="s">
+        <v>47</v>
+      </c>
+      <c r="M6" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1"/>
+    <hyperlink ref="B2" r:id="rId2"/>
+    <hyperlink ref="A3" r:id="rId3"/>
+    <hyperlink ref="B3" r:id="rId4"/>
+    <hyperlink ref="A4" r:id="rId5"/>
+    <hyperlink ref="B4" r:id="rId6"/>
+    <hyperlink ref="A5" r:id="rId7"/>
+    <hyperlink ref="B5" r:id="rId8"/>
+    <hyperlink ref="A6" r:id="rId9"/>
+    <hyperlink ref="B6" r:id="rId10"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>